--- a/output/laminas_comunales/comunal_i_peringr_median_a_2021_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2021_o_higgins.xlsx
@@ -1016,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1025,330 +1025,236 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chépica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>29.17</v>
+          <t>Marchigüe</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>24.47</v>
+          <t>Codegua</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codegua</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>16.65</v>
+          <t>Coinco</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coinco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>16.9</v>
+          <t>Coltauco</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coltauco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>20.38</v>
+          <t>Graneros</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Doñihue</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>13.93</v>
+          <t>Malloa</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Graneros</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>20.11</v>
+          <t>Peumo</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Estrella</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>16.94</v>
+          <t>Pichidegua</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>27.8</v>
+          <t>Rancagua</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Litueche</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>18.77</v>
+          <t>Requínoa</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lolol</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>26.98</v>
+          <t>Mostazal</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machalí</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>9.619999999999999</v>
+          <t>San Vicente</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Malloa</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>22.62</v>
+          <t>Nancagua</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mostazal</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>18.96</v>
+          <t>Peralillo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nancagua</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>23.26</v>
+          <t>Placilla</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Navidad</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>13.4</v>
+          <t>Pumanque</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Olivar</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>17.56</v>
+          <t>Paredones</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palmilla</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>23.63</v>
+          <t>Pichilemu</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paredones</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>28.85</v>
+          <t>Litueche</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Peralillo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>20.09</v>
+          <t>Navidad</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peumo</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>20.23</v>
+          <t>La Estrella</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>24.47</v>
+          <t>Doñihue</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>19.65</v>
+          <t>Olivar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Placilla</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>24.66</v>
+          <t>Rengo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pumanque</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>21.71</v>
+          <t>Santa Cruz</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>20.43</v>
+          <t>Palmilla</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rancagua</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>14.8</v>
+          <t>Quinta de Tilcoco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rengo</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>20.85</v>
+          <t>Machalí</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Requínoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>20.73</v>
+          <t>Las Cabras</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Fernando</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>18.79</v>
+          <t>Chimbarongo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>20.72</v>
+          <t>Lolol</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>22.05</v>
+          <t>Chépica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
       </c>
     </row>
   </sheetData>
